--- a/PTBR-COM-PORTRAIT/Lang/PTBR/Dialog/Drama/guild_doorman.xlsx
+++ b/PTBR-COM-PORTRAIT/Lang/PTBR/Dialog/Drama/guild_doorman.xlsx
@@ -446,9 +446,9 @@
           <t>Yes, I see you have brought the letter. Let me check.</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sim, vejo que você trouxe a carta. Deixe-me verificar.  </t>
+      <c r="L9" s="8" t="inlineStr">
+        <is>
+          <t>Sim, vejo que trouxe a carta. Deixa conferir.</t>
         </is>
       </c>
     </row>
@@ -471,9 +471,9 @@
           <t>Hmm, it certainly seems to be a letter of recommendation for the academy.</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Hmm, parece ser, de fato, uma carta de recomendação para a academia.  </t>
+      <c r="L10" s="8" t="inlineStr">
+        <is>
+          <t>Hum, certamente parece uma carta de recomendação para a academia.</t>
         </is>
       </c>
     </row>
@@ -547,9 +547,9 @@
           <t>It appears you have begun to learn the art of making darkness your ally. Congratulations. You are a formal member of the Thieves Guild now. You can now use this stairs to enter the office. Always conform to the guild's rule and perform your tasks.</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Parece que você começou a aprender a arte de fazer da escuridão sua aliada. Parabéns. Agora você é um membro oficial da Guilda dos Ladrões. Você pode usar estas escadas para entrar no escritório. Sempre siga as regras da guilda e cumpra suas tarefas.  </t>
+      <c r="L15" s="8" t="inlineStr">
+        <is>
+          <t>Vejo que começou a aprender a arte de fazer das trevas sua aliada. Parabéns. Você é um membro formal da Guilda dos Ladrões agora. Já pode usar esta escada para entrar no escritório. Siga sempre as regras da guilda e cumpra suas tarefas.</t>
         </is>
       </c>
     </row>
@@ -577,9 +577,9 @@
           <t>Congratulations. You are a formal member of the Mages Guild now. You can now use this stairs to enter the office. Always conform to the guild's rule and perform your tasks.</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Parabéns. Agora você é um membro oficial da Guilda dos Magos. Você pode usar estas escadas para entrar no escritório. Sempre siga as regras da guilda e cumpra suas tarefas.  </t>
+      <c r="L16" s="8" t="inlineStr">
+        <is>
+          <t>Parabéns. Você é um membro formal da Guilda dos Magos agora. Já pode usar esta escada para entrar no escritório. Siga sempre as regras da guilda e cumpra suas tarefas.</t>
         </is>
       </c>
     </row>
@@ -607,9 +607,9 @@
           <t>Congratulations. You are a formal member of the Fighters Guild now. You can now use this stairs to enter the office. Always conform to the guild's rule and perform your tasks.</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Parabéns. Agora você é um membro oficial da Guilda dos Lutadores. Você pode usar estas escadas para entrar no escritório. Sempre siga as regras da guilda e cumpra suas tarefas.  </t>
+      <c r="L17" s="8" t="inlineStr">
+        <is>
+          <t>Parabéns. Você é um membro formal da Guilda dos Lutadores agora. Já pode usar esta escada para entrar no escritório. Siga sempre as regras da guilda e cumpra suas tarefas.</t>
         </is>
       </c>
     </row>
@@ -653,9 +653,9 @@
           <t>Welcome to the Thieves Guild, #guild_title #pc... Please come in.</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bem-vindo à Guilda dos Ladrões, #guild_title #pc... Por favor, entre.  </t>
+      <c r="L20" s="8" t="inlineStr">
+        <is>
+          <t>Bem-vindo à Guilda dos Ladrões, #guild_title #pc... Entre, por favor.</t>
         </is>
       </c>
     </row>
@@ -683,9 +683,9 @@
           <t>Welcome to the Mages Guild, #guild_title #pc... Please come in.</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bem-vindo à Guilda dos Magos, #guild_title #pc... Por favor, entre.  </t>
+      <c r="L21" s="8" t="inlineStr">
+        <is>
+          <t>Bem-vindo à Guilda dos Magos, #guild_title #pc... Entre, por favor.</t>
         </is>
       </c>
     </row>
@@ -713,9 +713,9 @@
           <t>Welcome to the Fighters Guild, #guild_title #pc... Please come in.</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bem-vindo à Guilda dos Lutadores, #guild_title #pc... Por favor, entre.  </t>
+      <c r="L22" s="8" t="inlineStr">
+        <is>
+          <t>Bem-vindo à Guilda dos Lutadores, #guild_title #pc... Entre, por favor.</t>
         </is>
       </c>
     </row>
@@ -746,9 +746,9 @@
           <t>Halt...the door leads to the Thieves Guild office. Only the members of the guild are allowed to enter.</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>Aguarde... a porta leva ao escritório da Guilda dos Ladrões. Somente os membros da guilda têm permissão para entrar.</t>
+      <c r="L24" s="8" t="inlineStr">
+        <is>
+          <t>Alto lá...a porta leva ao escritório da Guilda dos Ladrões. Só membros da guilda podem entrar.</t>
         </is>
       </c>
     </row>
@@ -776,9 +776,9 @@
           <t>Halt...the door leads to the Mages Guild office. Only the members of the guild are allowed to enter.</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>Aguarde... a porta leva ao escritório da Guilda dos Magos. Somente os membros da guilda têm permissão para entrar.</t>
+      <c r="L25" s="8" t="inlineStr">
+        <is>
+          <t>Alto lá...a porta leva ao escritório da Guilda dos Magos. Só membros da guilda podem entrar.</t>
         </is>
       </c>
     </row>
@@ -806,9 +806,9 @@
           <t>Halt...the stairs lead to the Fighters Guild office. Only the members of the guild are allowed to enter.</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>Aguarde... as escadas levam ao escritório da Guilda dos Guerreiros. Somente os membros da guilda têm permissão para entrar.</t>
+      <c r="L26" s="8" t="inlineStr">
+        <is>
+          <t>Alto lá...a escada leva ao escritório da Guilda dos Lutadores. Só membros da guilda podem entrar.</t>
         </is>
       </c>
     </row>
@@ -844,9 +844,9 @@
           <t>Tell me about the Thieves Guild.</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>Fale-me sobre a Guilda dos Ladrões.</t>
+      <c r="L28" s="8" t="inlineStr">
+        <is>
+          <t>Fale-me da Guilda dos Ladrões.</t>
         </is>
       </c>
     </row>
@@ -879,9 +879,9 @@
           <t>Tell me about the Mages Guild.</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>Fale-me sobre a Guilda dos Magos.</t>
+      <c r="L29" s="8" t="inlineStr">
+        <is>
+          <t>Fale-me da Guilda dos Magos.</t>
         </is>
       </c>
     </row>
@@ -914,9 +914,9 @@
           <t>Tell me about the Fighters Guild.</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>Fale-me sobre a Guilda dos Guerreiros.</t>
+      <c r="L30" s="8" t="inlineStr">
+        <is>
+          <t>Fale-me da Guilda dos Lutadores.</t>
         </is>
       </c>
     </row>
@@ -954,9 +954,9 @@
           <t>I want to join the Thieves Guild.</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>Eu quero me juntar à Guilda dos Ladrões.</t>
+      <c r="L31" s="8" t="inlineStr">
+        <is>
+          <t>Quero entrar na Guilda dos Ladrões.</t>
         </is>
       </c>
     </row>
@@ -994,9 +994,9 @@
           <t>I want to join the Mages Guild.</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>Eu quero me juntar à Guilda dos Magos.</t>
+      <c r="L32" s="8" t="inlineStr">
+        <is>
+          <t>Quero entrar na Guilda dos Magos.</t>
         </is>
       </c>
     </row>
@@ -1034,9 +1034,9 @@
           <t>I want to join the Fighters Guild.</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>Eu quero me juntar à Guilda dos Guerreiros.</t>
+      <c r="L33" s="8" t="inlineStr">
+        <is>
+          <t>Quero entrar na Guilda dos Lutadores.</t>
         </is>
       </c>
     </row>
@@ -1107,10 +1107,10 @@
 We offer a variety of services such as buying stolen goods, discount at black markets, and training related skills. But joining the Thieves Guild requires you to pass a difficult test that most common thieves will fail.</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>Nossa Guilda dos Ladrões, "A Sombra da Noite", é composta por experientes e comprovados especialistas em sua área das artes sombrias.
-Oferecemos uma variedade de serviços, como compra de bens roubados, descontos em mercados negros e treinamento em habilidades relacionadas. Mas ingressar na Guilda dos Ladrões exige que você passe por um teste difícil, que a maioria dos ladrões comuns falhará.</t>
+      <c r="L41" s="8" t="inlineStr">
+        <is>
+          <t>Nossa Guilda dos Ladrões, "O Manto da Noite", é formada por experts experientes e comprovados nas artes das sombras.
+Oferecemos serviços variados: compra de bens roubados, desconto nos mercados negros e treino de perícias relacionadas. Mas entrar na Guilda dos Ladrões exige passar numa prova difícil que a maioria dos ladrões comuns reprova.</t>
         </is>
       </c>
     </row>
@@ -1135,11 +1135,10 @@
 We offer a variety of services such as discounted spellbook prices, reservation of spellbooks, and training related skills. Joining the Mages Guild only requires you to pass a simple trial.</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>A Guilda dos Magos é composta por experientes e comprovados especialistas em sua área da magia._x000D_
-_x000D_
-Oferecemos uma variedade de serviços, como preços com desconto para livros de feitiços, reserva de livros de feitiços e treinamento em habilidades relacionadas. Ingressar na Guilda dos Magos só exige que você passe por um teste simples.</t>
+      <c r="L42" s="8" t="inlineStr">
+        <is>
+          <t>A Guilda dos Magos é formada por experts experientes e comprovados no campo da magia.
+Oferecemos serviços variados: desconto em livros de feitiço, reserva de livros de feitiço e treino de perícias relacionadas. Entrar na Guilda dos Magos exige apenas passar numa prova simples.</t>
         </is>
       </c>
     </row>
@@ -1164,11 +1163,10 @@
 We offer a variety of services such as reduced prices of identification and restoring, and training related skills. But joining the Fighters Guild requires you to pass a difficult test that most common fighters will fail.</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>A Guilda dos Guerreiros é composta por experientes e comprovados especialistas em sua área da luta._x000D_
-_x000D_
-Oferecemos uma variedade de serviços, como preços reduzidos para identificação e restauração, e treinamento em habilidades relacionadas. Mas ingressar na Guilda dos Guerreiros exige que você passe por um teste difícil, que a maioria dos guerreiros comuns falhará.</t>
+      <c r="L43" s="8" t="inlineStr">
+        <is>
+          <t>A Guilda dos Lutadores é formada por experts experientes e comprovados no campo da luta.
+Oferecemos serviços variados: preço reduzido de identificação e restauração, e treino de perícias relacionadas. Mas entrar na Guilda dos Lutadores exige passar numa prova difícil que a maioria dos lutadores comuns reprova.</t>
         </is>
       </c>
     </row>
@@ -1216,9 +1214,9 @@
           <t>So...you're interested in our guild. We hide in the shadows of the society. You must win our trust to enter the guild.</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>Então... você está interessado em nossa guilda. Nos escondemos nas sombras da sociedade. Você deve conquistar nossa confiança para entrar na guilda.</t>
+      <c r="L49" s="8" t="inlineStr">
+        <is>
+          <t>Então...você está interessado na nossa guilda. Nós nos escondemos nas sombras da sociedade. Vai ter de conquistar nossa confiança para entrar.</t>
         </is>
       </c>
     </row>
@@ -1241,9 +1239,9 @@
           <t>So you are interested in joining us? Our academy is open to all who come seeking knowledge, regardless of class or talent. Of course, we will have to "review" you to see if you are worthy of being a member of  the Mages Guild.</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>Então você está interessado em se juntar a nós? Nossa academia está aberta a todos que busquem conhecimento, independentemente da classe ou talento. Claro, teremos que "avaliar" você para ver se é digno de ser um membro da Guilda dos Magos.</t>
+      <c r="L50" s="8" t="inlineStr">
+        <is>
+          <t>Então quer entrar? Nossa academia é aberta a todos que buscam conhecimento, sem importar classe ou talento. Claro, vamos ter de "avaliar" você para ver se é digno de ser membro da Guilda dos Magos.</t>
         </is>
       </c>
     </row>
@@ -1266,9 +1264,9 @@
           <t>To join the Fighters Guild, you must first face a test to earn our trust. We only need skilled hunters who will obey our law and remain undaunted even in a desperate battle.</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>Para se juntar à Guilda dos Guerreiros, você deve primeiro enfrentar um teste para conquistar nossa confiança. Só precisamos de caçadores habilidosos que irão obedecer nossa lei e permanecerão incansáveis, mesmo em uma batalha desesperadora.</t>
+      <c r="L51" s="8" t="inlineStr">
+        <is>
+          <t>Para entrar na Guilda dos Lutadores, primeiro tem de encarar uma prova para ganhar nossa confiança. Só precisamos de caçadores habilidosos que obedeçam nossa lei e não tremam nem numa batalha desesperada.</t>
         </is>
       </c>
     </row>
@@ -1299,7 +1297,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="L53" s="8" t="inlineStr">
         <is>
           <t>Sim</t>
         </is>
@@ -1329,7 +1327,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="L54" s="8" t="inlineStr">
         <is>
           <t>Não</t>
         </is>
@@ -1378,9 +1376,9 @@
           <t>The trial for the Thieves Guild is very simple. Those who wish to join "The Night Shroud"need only disobey the laws "they" have made. Rack up a record of crimes, break away from the foolish morals and customs that bind you, and immerse yourself in the world of darkness. "They" will hunt you down, of course. Your only allies are your own skills and the shadow. Come to me again when you eventually find peace in the shroud of night</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>O julgamento para a Guilda dos Ladrões é muito simples. Aqueles que desejam se juntar a "The Night Shroud" precisam apenas desobedecer às leis que "they" criaram. Acumule um histórico de crimes, rompa com as tolas morais e costumes que o prendem, e mergulhe no mundo da escuridão. "They" certamente o caçarão. Seus únicos aliados são suas próprias habilidades e a sombra. Volte a me procurar quando, eventualmente, encontrar paz no manto da noite</t>
+      <c r="L58" s="8" t="inlineStr">
+        <is>
+          <t>A prova da Guilda dos Ladrões é bem simples. Quem quiser entrar no "Manto da Noite" só precisa desobedecer as leis que "eles" fizeram. Acumule um histórico de crimes, afaste-se das moralidades e costumes tolos que te prendem, e mergulhe no mundo das trevas. "Eles" te caçarão, claro. Seus únicos aliados são suas próprias habilidades e a sombra. Volte a falar comigo quando finalmente achar paz no manto da noite</t>
         </is>
       </c>
     </row>
@@ -1403,9 +1401,9 @@
           <t>You don't have to be so formal in front of me. All you need to pass the review is a letter of recommendation from a Mages Guild member. If you don't know anyone who can give you the letter, you can always buy it from our sales-magician...I don't like the idea, but it's the guild master's decision.</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>Você não precisa ser tão formal na minha presença. Tudo o que você precisa para passar na avaliação é uma carta de recomendação de um membro da Guilda dos Magos. Se você não conhece ninguém que possa lhe fornecer a carta, sempre pode comprá-la do nosso sales-magician... Não gosto da ideia, mas é decisão do mestre da guilda.</t>
+      <c r="L59" s="8" t="inlineStr">
+        <is>
+          <t>Não precisa ser tão formal na minha frente. Tudo o que você precisa para passar na avaliação é uma carta de recomendação de um membro da Guilda dos Magos. Se não conhece ninguém que possa te dar a carta, sempre pode comprar do nosso mago-vendedor...Não gosto da ideia, mas é decisão do mestre da guilda.</t>
         </is>
       </c>
     </row>
@@ -1428,9 +1426,9 @@
           <t>Then let me give you the trial. One of the most common requests we receive is the extermination of the mischievous Yeeks. All the seasoned warriors in the guild are fed up with them. So I need you to kill about 20 of them for now. Report to me when you have finished the trial.</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>Então, deixe-me lhe propor o julgamento. Um dos pedidos mais comuns que recebemos é o extermínio dos travessos Yeeks. Todos os guerreiros experientes da guilda estão fartos deles. Então, preciso que você mate cerca de 20 deles, por enquanto. Informe-me quando você tiver terminado o julgamento.</t>
+      <c r="L60" s="8" t="inlineStr">
+        <is>
+          <t>Então deixe-me dar a prova. Um dos pedidos mais comuns que recebemos é o extermínio dos Yeeks chatos. Todos os guerreiros experientes da guilda estão de saco cheio deles. Então vá e mate cerca de 20 deles por enquanto.</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1482,7 @@
           <t>$chill</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
+      <c r="L65" s="8" t="inlineStr">
         <is>
           <t>$chill</t>
         </is>
